--- a/data/file_generation/input/data_223/店铺询盘转化趋势-1212.xlsx
+++ b/data/file_generation/input/data_223/店铺询盘转化趋势-1212.xlsx
@@ -28807,18 +28807,26 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
+  <documentManagement>
+    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB1E407D-E3E0-4718-ABD8-11B7D999FAB2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05E9BB81-E01D-457E-801E-E33FCA0C19CA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDF6BA6F-0EE6-498C-A959-7F015D886B14}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3ECB3D69-7246-488E-B571-FFE201CACB54}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80E001AA-B804-4961-AF9E-5DF04FF371FD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46E0827E-D9F3-4EE8-BDA9-79E7632FBDA6}"/>
 </file>